--- a/data/valuebets_database_2025-07-10.xlsx
+++ b/data/valuebets_database_2025-07-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>11/07 21:30</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>55</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45848.07851962763</v>
+        <v>45848.07851962963</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>11/07 16:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>60</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45848.07851962763</v>
+        <v>45848.07851962963</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>12/07 14:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>60</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45848.07851962763</v>
+        <v>45848.07851962963</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>13/07 14:30</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>60</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45848.07851962763</v>
+        <v>45848.07851962963</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>12/07 21:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>50</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45848.07851962763</v>
+        <v>45848.07851962963</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>11/07 12:30</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
+      <c r="F7" t="n">
+        <v>1.85</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45848.07851962763</v>
+        <v>45848.07851962963</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>12/07 19:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>45</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45848.07851962763</v>
+        <v>45848.07851962963</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>10/07 18:15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
+      <c r="F9" t="n">
+        <v>1.66</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45848.07851962763</v>
+        <v>45848.07851962963</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>14/07 19:15</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>40</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45848.07851962763</v>
+        <v>45848.07851962963</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>12/07 18:30</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>40</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45848.07851962763</v>
+        <v>45848.07851962963</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>10/07 10:20</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>4.45</t>
-        </is>
+      <c r="F12" t="n">
+        <v>4.45</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45848.07851962763</v>
+        <v>45848.07851962963</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>10/07 12:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
+      <c r="F13" t="n">
+        <v>5.5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,52 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45848.07851962763</v>
+        <v>45848.07851962963</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Club Améri</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Club América – Club TijuanaLiga MX</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>17/07 01:00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>+1,42%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>45848.14159514397</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-10.xlsx
+++ b/data/valuebets_database_2025-07-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1021,10 +1021,8 @@
           <t>17/07 01:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>45</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1037,7 +1035,52 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45848.14159514397</v>
+        <v>45848.14159513889</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Pas de buts | Legia Vars</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Legia Varsovie – AktobeEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>10/07 19:00</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>+3,13%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>45848.19083857376</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-10.xlsx
+++ b/data/valuebets_database_2025-07-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1064,10 +1064,8 @@
           <t>10/07 19:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>22.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>22</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1080,7 +1078,97 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45848.19083857376</v>
+        <v>45848.19083857639</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | X2 | Legia Vars</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Legia Varsovie – AktobeEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>10/07 19:00</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>25,3%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>+1,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>45848.226016787</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Club Boliv</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Club Bolivar – PalestinoCopa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>16/07 22:00</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>+0,94%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>45848.226016787</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-10.xlsx
+++ b/data/valuebets_database_2025-07-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1107,10 +1107,8 @@
           <t>10/07 19:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>4</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1123,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45848.226016787</v>
+        <v>45848.22601678241</v>
       </c>
     </row>
     <row r="17">
@@ -1152,10 +1150,8 @@
           <t>16/07 22:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>50</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1168,7 +1164,142 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45848.226016787</v>
+        <v>45848.22601678241</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Legia Vars</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Legia Varsovie – FC AktobeLigue Europa</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>10/07 19:00</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>+95,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>45848.27399056515</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | AEK Larnac</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AEK Larnaca – Partizan BelgradeLigue Europa</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>10/07 16:30</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>+40,6%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>45848.27399056515</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | 11-2- se qualifie | Spartak Tr</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Spartak Trnava – HäckenEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>11-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>10/07 18:15</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>33,8%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>+1,41%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>45848.27399056515</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-10.xlsx
+++ b/data/valuebets_database_2025-07-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1193,10 +1193,8 @@
           <t>10/07 19:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>110</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1209,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45848.27399056515</v>
+        <v>45848.27399056713</v>
       </c>
     </row>
     <row r="19">
@@ -1238,10 +1236,8 @@
           <t>10/07 16:30</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>60</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1254,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45848.27399056515</v>
+        <v>45848.27399056713</v>
       </c>
     </row>
     <row r="20">
@@ -1283,10 +1279,8 @@
           <t>10/07 18:15</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>3</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1299,7 +1293,52 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45848.27399056515</v>
+        <v>45848.27399056713</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Bwin(FR)Football | 2 / HNB | Angleterre</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bwin(FR)Football</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Angleterre (F) – Pays de Galles (F)Europe - Euro (F)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2 / HNB</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>13/07 19:00</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>29,0%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>+10,3%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>45848.30768396214</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-10.xlsx
+++ b/data/valuebets_database_2025-07-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1322,10 +1322,8 @@
           <t>13/07 19:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
+      <c r="F21" t="n">
+        <v>3.8</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1338,7 +1336,142 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45848.30768396214</v>
+        <v>45848.30768395833</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 11.5 - tirs2e équipe | Norvège F.</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Norvège F. – Islande F.Europe - Euro Féminin 2025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Moins que 11.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>10/07 19:00</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>53,8%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>+26,4%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>45848.35488343815</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 13.5 - tirs2e équipe | Finlande F</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Finlande F. – Suisse F.Europe - Euro Féminin 2025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Moins que 13.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>10/07 19:00</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>46,0%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>+4,80%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>45848.35488343815</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | Moins que 9.52e set | T.Fritz – </t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>T.Fritz – C.AlcarazATP - Wimbledon H</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Moins que 9.52e set</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>11/07 12:30</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>40,0%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>+0,00%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>45848.35488343815</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-10.xlsx
+++ b/data/valuebets_database_2025-07-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1365,10 +1365,8 @@
           <t>10/07 19:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="F22" t="n">
+        <v>2.35</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1381,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45848.35488343815</v>
+        <v>45848.3548834375</v>
       </c>
     </row>
     <row r="23">
@@ -1410,10 +1408,8 @@
           <t>10/07 19:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2.28</t>
-        </is>
+      <c r="F23" t="n">
+        <v>2.28</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1426,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45848.35488343815</v>
+        <v>45848.3548834375</v>
       </c>
     </row>
     <row r="24">
@@ -1455,10 +1451,8 @@
           <t>11/07 12:30</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F24" t="n">
+        <v>2.5</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1471,7 +1465,97 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45848.35488343815</v>
+        <v>45848.3548834375</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Finlande –</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Finlande – SuisseUEFA Euro (F) - Matchs</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>10/07 19:00</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>+2,42%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>45848.39346967722</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PokerStars(FR)Basketball | X2e période[race to 15 regular time] | Las Vegas </t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces – Washington MysticsUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>X2e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>10/07 23:30</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>5,30%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+0,66%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45848.39346967722</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-10.xlsx
+++ b/data/valuebets_database_2025-07-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1494,10 +1494,8 @@
           <t>10/07 19:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>40</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1510,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45848.39346967722</v>
+        <v>45848.39346967592</v>
       </c>
     </row>
     <row r="26">
@@ -1539,10 +1537,8 @@
           <t>10/07 23:30</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>19.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>19</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1555,7 +1551,52 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45848.39346967722</v>
+        <v>45848.39346967592</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FC Sheriff</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>FC Sheriff Tiraspol – FC PrishtinaLigue Europa</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>10/07 17:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>90.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+41,7%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45848.43421639116</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-10.xlsx
+++ b/data/valuebets_database_2025-07-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>10/07 17:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>90.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>90</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,142 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45848.43421639116</v>
+        <v>45848.43421638889</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Shakhtar D</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Shakhtar Donetsk – FC IlvesLigue Europa</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>10/07 18:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+366%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45848.47208721164</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 21-2- se qualifie | AEK Larnac</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AEK Larnaca – Partizan BelgradeEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>10/07 16:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>37,0%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+1,83%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45848.47208721164</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 21-2- se qualifie | Paksi – CF</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Paksi – CFR ClujEurope. Europa League (Q)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>10/07 17:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>79,5%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+0,16%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45848.47208721164</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-10.xlsx
+++ b/data/valuebets_database_2025-07-10.xlsx
@@ -1623,10 +1623,8 @@
           <t>10/07 18:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>200</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1639,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45848.47208721164</v>
+        <v>45848.47208721065</v>
       </c>
     </row>
     <row r="29">
@@ -1668,10 +1666,8 @@
           <t>10/07 16:30</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F29" t="n">
+        <v>2.75</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1684,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45848.47208721164</v>
+        <v>45848.47208721065</v>
       </c>
     </row>
     <row r="30">
@@ -1713,10 +1709,8 @@
           <t>10/07 17:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
+      <c r="F30" t="n">
+        <v>1.26</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1729,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45848.47208721164</v>
+        <v>45848.47208721065</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-10.xlsx
+++ b/data/valuebets_database_2025-07-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1726,6 +1726,276 @@
         <v>45848.47208721065</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Gimnasia L</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Gimnasia La Plata – Instituto AC CordobaLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>12/07 21:30</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+30,3%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45848.59972443592</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | CA Sarmien</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CA Sarmiento – CA IndependienteLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>13/07 17:15</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+19,6%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45848.59972443592</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.51re équipe | Deportivo </t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra – Atletico LanusLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>14/07 19:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+13,3%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45848.59972443592</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | Talleres d</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Talleres de Cordoba – San LorenzoLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>11/07 23:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+12,2%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45848.59972443592</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Plus que 5.5 - aces | Belinda Be</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Belinda Bencic – Iga SwiatekWTA - Wimbledon</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Plus que 5.5 - aces</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>10/07 14:40</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>53,2%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+1,06%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45848.59972443592</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Bohemians </t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Bohemians – Galway UnitedPremier Division</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>11/07 18:45</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+0,40%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45848.59972443592</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-10.xlsx
+++ b/data/valuebets_database_2025-07-10.xlsx
@@ -1752,10 +1752,8 @@
           <t>12/07 21:30</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>60</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45848.59972443592</v>
+        <v>45848.59972443287</v>
       </c>
     </row>
     <row r="32">
@@ -1797,10 +1795,8 @@
           <t>13/07 17:15</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>50</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1813,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45848.59972443592</v>
+        <v>45848.59972443287</v>
       </c>
     </row>
     <row r="33">
@@ -1842,10 +1838,8 @@
           <t>14/07 19:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>50</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1858,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45848.59972443592</v>
+        <v>45848.59972443287</v>
       </c>
     </row>
     <row r="34">
@@ -1887,10 +1881,8 @@
           <t>11/07 23:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>55</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1903,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45848.59972443592</v>
+        <v>45848.59972443287</v>
       </c>
     </row>
     <row r="35">
@@ -1932,10 +1924,8 @@
           <t>10/07 14:40</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
+      <c r="F35" t="n">
+        <v>1.9</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1948,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45848.59972443592</v>
+        <v>45848.59972443287</v>
       </c>
     </row>
     <row r="36">
@@ -1977,10 +1967,8 @@
           <t>11/07 18:45</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>40</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1993,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45848.59972443592</v>
+        <v>45848.59972443287</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-10.xlsx
+++ b/data/valuebets_database_2025-07-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1984,6 +1984,96 @@
         <v>45848.59972443287</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 13.5 - tirs2e équipe | Norvège F.</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Norvège F. – Islande F.Europe - Euro Féminin 2025</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Moins que 13.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>10/07 19:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>65,8%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+1,36%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45848.77244099219</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 1 | Botev Plov</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Botev Plovdiv – CSKA SofiaBulgarie. Bulgarie - Parva Liga</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>19/07 16:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>18,2%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+0,32%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45848.77244099219</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-10.xlsx
+++ b/data/valuebets_database_2025-07-10.xlsx
@@ -2010,10 +2010,8 @@
           <t>10/07 19:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
+      <c r="F37" t="n">
+        <v>1.54</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2026,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45848.77244099219</v>
+        <v>45848.77244099537</v>
       </c>
     </row>
     <row r="38">
@@ -2055,10 +2053,8 @@
           <t>19/07 16:00</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
+      <c r="F38" t="n">
+        <v>5.5</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2071,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45848.77244099219</v>
+        <v>45848.77244099537</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-10.xlsx
+++ b/data/valuebets_database_2025-07-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2070,6 +2070,51 @@
         <v>45848.77244099537</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Independie</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Independiente Del Valle – Vasco da GamaCopa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>16/07 00:30</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+0,94%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45848.85105721186</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-10.xlsx
+++ b/data/valuebets_database_2025-07-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,10 +2096,8 @@
           <t>16/07 00:30</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>45</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2112,7 +2110,52 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45848.85105721186</v>
+        <v>45848.85105721065</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Inter Club</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Inter Club de Escaldes – FCSBLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>15/07 18:30</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+30,6%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45848.89118531982</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-10.xlsx
+++ b/data/valuebets_database_2025-07-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,23 +2139,291 @@
           <t>15/07 18:30</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" t="n">
+        <v>60</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+30,6%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45848.89118532407</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Godoy Cruz – CA SarmientoLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>19/07 21:45</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>+30,6%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>45848.89118531982</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+20,6%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45848.93160113464</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CA Tigre –</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CA Tigre – Argentinos JuniorsLiga Profesional stq pr cu 385076e7</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>20/07 13:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+20,0%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45848.93160113464</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.51re équipe | Instituto </t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Instituto AC Cordoba – River PlateLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>20/07 00:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+19,0%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45848.93160113464</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Fagiano Ok</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Fagiano Okayama – Vissel KobeJ-League</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>20/07 10:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+16,8%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45848.93160113464</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Defensa y </t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Defensa y Justicia – CA AldosiviLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>20/07 13:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+5,71%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45848.93160113464</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CA Platens</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CA Platense – Velez SarsfieldLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>19/07 21:45</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+0,53%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45848.93160113464</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-10.xlsx
+++ b/data/valuebets_database_2025-07-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2182,10 +2182,8 @@
           <t>19/07 21:45</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>60</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2198,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45848.93160113464</v>
+        <v>45848.93160113426</v>
       </c>
     </row>
     <row r="42">
@@ -2227,10 +2225,8 @@
           <t>20/07 13:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>45</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2243,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45848.93160113464</v>
+        <v>45848.93160113426</v>
       </c>
     </row>
     <row r="43">
@@ -2272,10 +2268,8 @@
           <t>20/07 00:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>50</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2288,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45848.93160113464</v>
+        <v>45848.93160113426</v>
       </c>
     </row>
     <row r="44">
@@ -2317,10 +2311,8 @@
           <t>20/07 10:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>60</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2333,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45848.93160113464</v>
+        <v>45848.93160113426</v>
       </c>
     </row>
     <row r="45">
@@ -2362,10 +2354,8 @@
           <t>20/07 13:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>40</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2378,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45848.93160113464</v>
+        <v>45848.93160113426</v>
       </c>
     </row>
     <row r="46">
@@ -2407,23 +2397,111 @@
           <t>19/07 21:45</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" t="n">
+        <v>45</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+0,53%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45848.93160113426</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Orlando Ci</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Orlando City – CF MontréalMLS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>12/07 23:30</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>45.00</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>+0,53%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>45848.93160113464</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+11,0%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45848.97353210411</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Tokyo Verd</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Tokyo Verdy – Machida ZelviaJ-League</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>20/07 09:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+6,58%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45848.97353210411</v>
       </c>
     </row>
   </sheetData>
